--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532081</v>
+        <v>121532090</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458962</v>
+        <v>459113</v>
       </c>
       <c r="R2" t="n">
-        <v>7081129</v>
+        <v>7081080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +780,7 @@
         <v>121532080</v>
       </c>
       <c r="B3" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532090</v>
+        <v>121532081</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459113</v>
+        <v>458962</v>
       </c>
       <c r="R4" t="n">
-        <v>7081080</v>
+        <v>7081129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532090</v>
+        <v>121532080</v>
       </c>
       <c r="B2" t="n">
-        <v>90737</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459113</v>
+        <v>459027</v>
       </c>
       <c r="R2" t="n">
-        <v>7081080</v>
+        <v>7081121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532080</v>
+        <v>121532081</v>
       </c>
       <c r="B3" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459027</v>
+        <v>458962</v>
       </c>
       <c r="R3" t="n">
-        <v>7081121</v>
+        <v>7081129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532081</v>
+        <v>121532090</v>
       </c>
       <c r="B4" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458962</v>
+        <v>459113</v>
       </c>
       <c r="R4" t="n">
-        <v>7081129</v>
+        <v>7081080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532080</v>
+        <v>121532081</v>
       </c>
       <c r="B2" t="n">
         <v>57356</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459027</v>
+        <v>458962</v>
       </c>
       <c r="R2" t="n">
-        <v>7081121</v>
+        <v>7081129</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532081</v>
+        <v>121532090</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458962</v>
+        <v>459113</v>
       </c>
       <c r="R3" t="n">
-        <v>7081129</v>
+        <v>7081080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532090</v>
+        <v>121532080</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459113</v>
+        <v>459027</v>
       </c>
       <c r="R4" t="n">
-        <v>7081080</v>
+        <v>7081121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532081</v>
+        <v>121532090</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458962</v>
+        <v>459113</v>
       </c>
       <c r="R2" t="n">
-        <v>7081129</v>
+        <v>7081080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532090</v>
+        <v>121532080</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459113</v>
+        <v>459027</v>
       </c>
       <c r="R3" t="n">
-        <v>7081080</v>
+        <v>7081121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532080</v>
+        <v>121532081</v>
       </c>
       <c r="B4" t="n">
         <v>57356</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459027</v>
+        <v>458962</v>
       </c>
       <c r="R4" t="n">
-        <v>7081121</v>
+        <v>7081129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532090</v>
+        <v>121532080</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459113</v>
+        <v>459027</v>
       </c>
       <c r="R2" t="n">
-        <v>7081080</v>
+        <v>7081121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532080</v>
+        <v>121532090</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459027</v>
+        <v>459113</v>
       </c>
       <c r="R3" t="n">
-        <v>7081121</v>
+        <v>7081080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532080</v>
+        <v>121532090</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459027</v>
+        <v>459113</v>
       </c>
       <c r="R2" t="n">
-        <v>7081121</v>
+        <v>7081080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532090</v>
+        <v>121532081</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459113</v>
+        <v>458962</v>
       </c>
       <c r="R3" t="n">
-        <v>7081080</v>
+        <v>7081129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532081</v>
+        <v>121532080</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458962</v>
+        <v>459027</v>
       </c>
       <c r="R4" t="n">
-        <v>7081129</v>
+        <v>7081121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532090</v>
+        <v>121532081</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459113</v>
+        <v>458962</v>
       </c>
       <c r="R2" t="n">
-        <v>7081080</v>
+        <v>7081129</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532080</v>
+        <v>121532090</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459027</v>
+        <v>459113</v>
       </c>
       <c r="R3" t="n">
-        <v>7081121</v>
+        <v>7081080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121532081</v>
+        <v>121532080</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458962</v>
+        <v>459027</v>
       </c>
       <c r="R4" t="n">
-        <v>7081129</v>
+        <v>7081121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47838-2024 artfynd.xlsx
+++ b/artfynd/A 47838-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121532081</v>
+        <v>121532090</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458962</v>
+        <v>459113</v>
       </c>
       <c r="R2" t="n">
-        <v>7081129</v>
+        <v>7081080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121532090</v>
+        <v>121532081</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459113</v>
+        <v>458962</v>
       </c>
       <c r="R3" t="n">
-        <v>7081080</v>
+        <v>7081129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
